--- a/output/yearly_population_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_32_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6121</v>
+        <v>5578</v>
       </c>
       <c r="C2" t="n">
-        <v>7980</v>
+        <v>4748</v>
       </c>
       <c r="D2" t="n">
-        <v>27200</v>
+        <v>17592</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3283</v>
+        <v>3755</v>
       </c>
       <c r="C3" t="n">
-        <v>6040</v>
+        <v>3668</v>
       </c>
       <c r="D3" t="n">
-        <v>15733</v>
+        <v>11692</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2553</v>
+        <v>3016</v>
       </c>
       <c r="C4" t="n">
-        <v>5089</v>
+        <v>3817</v>
       </c>
       <c r="D4" t="n">
-        <v>6258</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1590</v>
+        <v>2001</v>
       </c>
       <c r="C5" t="n">
-        <v>5045</v>
+        <v>3783</v>
       </c>
       <c r="D5" t="n">
-        <v>2233</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>3331</v>
+        <v>2301</v>
       </c>
       <c r="D6" t="n">
-        <v>1028</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>441</v>
+        <v>545</v>
       </c>
       <c r="C7" t="n">
-        <v>1918</v>
+        <v>1073</v>
       </c>
       <c r="D7" t="n">
-        <v>642</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C8" t="n">
-        <v>887</v>
+        <v>504</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5930</v>
+        <v>8509</v>
       </c>
       <c r="C2" t="n">
-        <v>10114</v>
+        <v>10542</v>
       </c>
       <c r="D2" t="n">
-        <v>31258</v>
+        <v>18005</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3678</v>
+        <v>3755</v>
       </c>
       <c r="C3" t="n">
-        <v>6091</v>
+        <v>3668</v>
       </c>
       <c r="D3" t="n">
-        <v>16235</v>
+        <v>11737</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2479</v>
+        <v>2872</v>
       </c>
       <c r="C4" t="n">
-        <v>5390</v>
+        <v>3625</v>
       </c>
       <c r="D4" t="n">
-        <v>7614</v>
+        <v>6917</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1766</v>
+        <v>2195</v>
       </c>
       <c r="C5" t="n">
-        <v>4960</v>
+        <v>3721</v>
       </c>
       <c r="D5" t="n">
-        <v>2761</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1090</v>
+        <v>1399</v>
       </c>
       <c r="C6" t="n">
-        <v>4039</v>
+        <v>2988</v>
       </c>
       <c r="D6" t="n">
-        <v>1199</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>577</v>
+        <v>734</v>
       </c>
       <c r="C7" t="n">
-        <v>2554</v>
+        <v>1639</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>313</v>
       </c>
       <c r="C8" t="n">
-        <v>1322</v>
+        <v>765</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C9" t="n">
-        <v>577</v>
+        <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
         <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6048</v>
+        <v>10186</v>
       </c>
       <c r="C2" t="n">
-        <v>17126</v>
+        <v>7991</v>
       </c>
       <c r="D2" t="n">
-        <v>29565</v>
+        <v>16184</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3745</v>
+        <v>4678</v>
       </c>
       <c r="C3" t="n">
-        <v>6938</v>
+        <v>5928</v>
       </c>
       <c r="D3" t="n">
-        <v>17248</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2521</v>
+        <v>2779</v>
       </c>
       <c r="C4" t="n">
-        <v>5528</v>
+        <v>3535</v>
       </c>
       <c r="D4" t="n">
-        <v>8550</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1842</v>
+        <v>2236</v>
       </c>
       <c r="C5" t="n">
-        <v>4990</v>
+        <v>3599</v>
       </c>
       <c r="D5" t="n">
-        <v>3349</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1235</v>
+        <v>1585</v>
       </c>
       <c r="C6" t="n">
-        <v>4382</v>
+        <v>3253</v>
       </c>
       <c r="D6" t="n">
-        <v>1408</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>699</v>
+        <v>912</v>
       </c>
       <c r="C7" t="n">
-        <v>3124</v>
+        <v>2233</v>
       </c>
       <c r="D7" t="n">
-        <v>741</v>
+        <v>826</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>334</v>
+        <v>435</v>
       </c>
       <c r="C8" t="n">
-        <v>1791</v>
+        <v>1125</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>861</v>
+        <v>534</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>376</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5675</v>
+        <v>9038</v>
       </c>
       <c r="C2" t="n">
-        <v>11645</v>
+        <v>5178</v>
       </c>
       <c r="D2" t="n">
-        <v>24479</v>
+        <v>13157</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4509</v>
+        <v>5476</v>
       </c>
       <c r="C3" t="n">
-        <v>10997</v>
+        <v>8229</v>
       </c>
       <c r="D3" t="n">
-        <v>18356</v>
+        <v>13275</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1702</v>
+        <v>2066</v>
       </c>
       <c r="C4" t="n">
-        <v>7815</v>
+        <v>5525</v>
       </c>
       <c r="D4" t="n">
-        <v>7896</v>
+        <v>7410</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1141</v>
+        <v>1464</v>
       </c>
       <c r="C5" t="n">
-        <v>4294</v>
+        <v>3187</v>
       </c>
       <c r="D5" t="n">
-        <v>2280</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>645</v>
+        <v>842</v>
       </c>
       <c r="C6" t="n">
-        <v>3061</v>
+        <v>2188</v>
       </c>
       <c r="D6" t="n">
-        <v>726</v>
+        <v>809</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>401</v>
       </c>
       <c r="C7" t="n">
-        <v>1755</v>
+        <v>1102</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="C8" t="n">
-        <v>843</v>
+        <v>523</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3541</v>
+        <v>5267</v>
       </c>
       <c r="C2" t="n">
-        <v>5847</v>
+        <v>2165</v>
       </c>
       <c r="D2" t="n">
-        <v>16766</v>
+        <v>10219</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4351</v>
+        <v>6048</v>
       </c>
       <c r="C3" t="n">
-        <v>10240</v>
+        <v>6070</v>
       </c>
       <c r="D3" t="n">
-        <v>18307</v>
+        <v>12472</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2393</v>
+        <v>2993</v>
       </c>
       <c r="C4" t="n">
-        <v>9343</v>
+        <v>6972</v>
       </c>
       <c r="D4" t="n">
-        <v>9238</v>
+        <v>8284</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1279</v>
+        <v>1629</v>
       </c>
       <c r="C5" t="n">
-        <v>5864</v>
+        <v>4306</v>
       </c>
       <c r="D5" t="n">
-        <v>2955</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>764</v>
+        <v>1020</v>
       </c>
       <c r="C6" t="n">
-        <v>3673</v>
+        <v>2694</v>
       </c>
       <c r="D6" t="n">
-        <v>887</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="C7" t="n">
-        <v>2237</v>
+        <v>1507</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1122</v>
+        <v>711</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4075</v>
+        <v>5824</v>
       </c>
       <c r="C2" t="n">
-        <v>10820</v>
+        <v>5026</v>
       </c>
       <c r="D2" t="n">
-        <v>16607</v>
+        <v>9982</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3376</v>
+        <v>4823</v>
       </c>
       <c r="C3" t="n">
-        <v>7202</v>
+        <v>3574</v>
       </c>
       <c r="D3" t="n">
-        <v>16867</v>
+        <v>11371</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2783</v>
+        <v>3746</v>
       </c>
       <c r="C4" t="n">
-        <v>9587</v>
+        <v>6417</v>
       </c>
       <c r="D4" t="n">
-        <v>10437</v>
+        <v>8755</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1542</v>
+        <v>1989</v>
       </c>
       <c r="C5" t="n">
-        <v>7434</v>
+        <v>5547</v>
       </c>
       <c r="D5" t="n">
-        <v>3830</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>893</v>
+        <v>1199</v>
       </c>
       <c r="C6" t="n">
-        <v>4605</v>
+        <v>3466</v>
       </c>
       <c r="D6" t="n">
-        <v>1173</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>577</v>
       </c>
       <c r="C7" t="n">
-        <v>2877</v>
+        <v>2067</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="C8" t="n">
-        <v>1580</v>
+        <v>1060</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>680</v>
+        <v>494</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2433</v>
+        <v>3355</v>
       </c>
       <c r="C2" t="n">
-        <v>5162</v>
+        <v>2199</v>
       </c>
       <c r="D2" t="n">
-        <v>11639</v>
+        <v>6854</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3415</v>
+        <v>4901</v>
       </c>
       <c r="C3" t="n">
-        <v>8181</v>
+        <v>3976</v>
       </c>
       <c r="D3" t="n">
-        <v>16462</v>
+        <v>10913</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3044</v>
+        <v>4202</v>
       </c>
       <c r="C4" t="n">
-        <v>9552</v>
+        <v>5862</v>
       </c>
       <c r="D4" t="n">
-        <v>11213</v>
+        <v>9185</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1595</v>
+        <v>2112</v>
       </c>
       <c r="C5" t="n">
-        <v>8983</v>
+        <v>6515</v>
       </c>
       <c r="D5" t="n">
-        <v>4067</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>742</v>
+        <v>1053</v>
       </c>
       <c r="C6" t="n">
-        <v>5529</v>
+        <v>4395</v>
       </c>
       <c r="D6" t="n">
-        <v>1160</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>2957</v>
+        <v>2123</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1146</v>
+        <v>837</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2682</v>
+        <v>4128</v>
       </c>
       <c r="C2" t="n">
-        <v>7425</v>
+        <v>4396</v>
       </c>
       <c r="D2" t="n">
-        <v>11679</v>
+        <v>10865</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2582</v>
+        <v>3602</v>
       </c>
       <c r="C3" t="n">
-        <v>6107</v>
+        <v>2743</v>
       </c>
       <c r="D3" t="n">
-        <v>14857</v>
+        <v>9577</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2791</v>
+        <v>3937</v>
       </c>
       <c r="C4" t="n">
-        <v>8721</v>
+        <v>4836</v>
       </c>
       <c r="D4" t="n">
-        <v>11678</v>
+        <v>9204</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1924</v>
+        <v>2664</v>
       </c>
       <c r="C5" t="n">
-        <v>9133</v>
+        <v>6128</v>
       </c>
       <c r="D5" t="n">
-        <v>4972</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>1364</v>
       </c>
       <c r="C6" t="n">
-        <v>6959</v>
+        <v>5351</v>
       </c>
       <c r="D6" t="n">
-        <v>1535</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>420</v>
       </c>
       <c r="C7" t="n">
-        <v>4021</v>
+        <v>3143</v>
       </c>
       <c r="D7" t="n">
-        <v>642</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>1806</v>
+        <v>1357</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
         <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1892</v>
+        <v>3016</v>
       </c>
       <c r="C2" t="n">
-        <v>4901</v>
+        <v>2810</v>
       </c>
       <c r="D2" t="n">
-        <v>9610</v>
+        <v>8222</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2291</v>
+        <v>3311</v>
       </c>
       <c r="C3" t="n">
-        <v>6072</v>
+        <v>3110</v>
       </c>
       <c r="D3" t="n">
-        <v>13810</v>
+        <v>9205</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2516</v>
+        <v>3494</v>
       </c>
       <c r="C4" t="n">
-        <v>7761</v>
+        <v>3950</v>
       </c>
       <c r="D4" t="n">
-        <v>11831</v>
+        <v>9066</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2063</v>
+        <v>2939</v>
       </c>
       <c r="C5" t="n">
-        <v>9063</v>
+        <v>5727</v>
       </c>
       <c r="D5" t="n">
-        <v>5624</v>
+        <v>5508</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1127</v>
+        <v>1635</v>
       </c>
       <c r="C6" t="n">
-        <v>7901</v>
+        <v>5834</v>
       </c>
       <c r="D6" t="n">
-        <v>1810</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>4986</v>
+        <v>3963</v>
       </c>
       <c r="D7" t="n">
-        <v>709</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>2323</v>
+        <v>1813</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>640</v>
+        <v>606</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2413</v>
+        <v>5406</v>
       </c>
       <c r="C2" t="n">
-        <v>8853</v>
+        <v>4847</v>
       </c>
       <c r="D2" t="n">
-        <v>10577</v>
+        <v>17737</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1813</v>
+        <v>2685</v>
       </c>
       <c r="C3" t="n">
-        <v>5008</v>
+        <v>2631</v>
       </c>
       <c r="D3" t="n">
-        <v>12554</v>
+        <v>8475</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2140</v>
+        <v>2975</v>
       </c>
       <c r="C4" t="n">
-        <v>6902</v>
+        <v>3480</v>
       </c>
       <c r="D4" t="n">
-        <v>11623</v>
+        <v>8811</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2020</v>
+        <v>2893</v>
       </c>
       <c r="C5" t="n">
-        <v>8362</v>
+        <v>4823</v>
       </c>
       <c r="D5" t="n">
-        <v>6287</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1332</v>
+        <v>1965</v>
       </c>
       <c r="C6" t="n">
-        <v>8271</v>
+        <v>5735</v>
       </c>
       <c r="D6" t="n">
-        <v>2262</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>456</v>
+        <v>751</v>
       </c>
       <c r="C7" t="n">
-        <v>6089</v>
+        <v>4770</v>
       </c>
       <c r="D7" t="n">
-        <v>831</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>3209</v>
+        <v>2651</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>1173</v>
+        <v>1031</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>41</v>
+      </c>
+      <c r="D14" t="n">
         <v>39</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5264</v>
+        <v>5391</v>
       </c>
       <c r="C2" t="n">
-        <v>5209</v>
+        <v>2983</v>
       </c>
       <c r="D2" t="n">
-        <v>8429</v>
+        <v>15770</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1764</v>
+        <v>3743</v>
       </c>
       <c r="C2" t="n">
-        <v>5171</v>
+        <v>2636</v>
       </c>
       <c r="D2" t="n">
-        <v>7869</v>
+        <v>12912</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2429</v>
+        <v>3780</v>
       </c>
       <c r="C3" t="n">
-        <v>6287</v>
+        <v>3412</v>
       </c>
       <c r="D3" t="n">
-        <v>13536</v>
+        <v>9920</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2960</v>
+        <v>4160</v>
       </c>
       <c r="C4" t="n">
-        <v>9787</v>
+        <v>5037</v>
       </c>
       <c r="D4" t="n">
-        <v>11774</v>
+        <v>9231</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>1976</v>
       </c>
       <c r="C5" t="n">
-        <v>11944</v>
+        <v>7614</v>
       </c>
       <c r="D5" t="n">
-        <v>5657</v>
+        <v>5505</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>421</v>
+        <v>693</v>
       </c>
       <c r="C6" t="n">
-        <v>7426</v>
+        <v>5967</v>
       </c>
       <c r="D6" t="n">
-        <v>1794</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>3144</v>
+        <v>2597</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1149</v>
+        <v>1010</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6485</v>
+        <v>7680</v>
       </c>
       <c r="C2" t="n">
-        <v>8635</v>
+        <v>3173</v>
       </c>
       <c r="D2" t="n">
-        <v>11017</v>
+        <v>16112</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2237</v>
+        <v>2291</v>
       </c>
       <c r="C3" t="n">
-        <v>2667</v>
+        <v>1503</v>
       </c>
       <c r="D3" t="n">
-        <v>2055</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3930</v>
+        <v>5179</v>
       </c>
       <c r="C2" t="n">
-        <v>6637</v>
+        <v>3634</v>
       </c>
       <c r="D2" t="n">
-        <v>13277</v>
+        <v>14315</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3579</v>
+        <v>4089</v>
       </c>
       <c r="C3" t="n">
-        <v>5255</v>
+        <v>2122</v>
       </c>
       <c r="D3" t="n">
-        <v>3409</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1005</v>
+        <v>1029</v>
       </c>
       <c r="C4" t="n">
-        <v>1631</v>
+        <v>939</v>
       </c>
       <c r="D4" t="n">
-        <v>1595</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3648</v>
+        <v>5582</v>
       </c>
       <c r="C2" t="n">
-        <v>5178</v>
+        <v>5612</v>
       </c>
       <c r="D2" t="n">
-        <v>15518</v>
+        <v>13934</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3095</v>
+        <v>3848</v>
       </c>
       <c r="C3" t="n">
-        <v>5201</v>
+        <v>2550</v>
       </c>
       <c r="D3" t="n">
-        <v>4742</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1939</v>
+        <v>2162</v>
       </c>
       <c r="C4" t="n">
-        <v>3649</v>
+        <v>1580</v>
       </c>
       <c r="D4" t="n">
-        <v>1894</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="C5" t="n">
-        <v>985</v>
+        <v>616</v>
       </c>
       <c r="D5" t="n">
-        <v>1213</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5274,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>211</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5004</v>
+        <v>5859</v>
       </c>
       <c r="C2" t="n">
-        <v>11225</v>
+        <v>9174</v>
       </c>
       <c r="D2" t="n">
-        <v>19662</v>
+        <v>20362</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2769</v>
+        <v>3848</v>
       </c>
       <c r="C3" t="n">
-        <v>4508</v>
+        <v>3611</v>
       </c>
       <c r="D3" t="n">
-        <v>6046</v>
+        <v>7004</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2131</v>
+        <v>2568</v>
       </c>
       <c r="C4" t="n">
-        <v>4422</v>
+        <v>2077</v>
       </c>
       <c r="D4" t="n">
-        <v>2337</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1004</v>
+        <v>1092</v>
       </c>
       <c r="C5" t="n">
-        <v>2371</v>
+        <v>1106</v>
       </c>
       <c r="D5" t="n">
-        <v>1300</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C6" t="n">
-        <v>643</v>
+        <v>461</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>218</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>123</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5675,7 +5675,7 @@
         <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6203</v>
+        <v>7006</v>
       </c>
       <c r="C2" t="n">
-        <v>8538</v>
+        <v>6110</v>
       </c>
       <c r="D2" t="n">
-        <v>36014</v>
+        <v>23671</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2816</v>
+        <v>3527</v>
       </c>
       <c r="C3" t="n">
-        <v>6555</v>
+        <v>5328</v>
       </c>
       <c r="D3" t="n">
-        <v>7234</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1531</v>
+        <v>1990</v>
       </c>
       <c r="C4" t="n">
-        <v>3666</v>
+        <v>2393</v>
       </c>
       <c r="D4" t="n">
-        <v>2546</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>819</v>
+        <v>965</v>
       </c>
       <c r="C5" t="n">
-        <v>2526</v>
+        <v>1192</v>
       </c>
       <c r="D5" t="n">
-        <v>1175</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C6" t="n">
-        <v>1015</v>
+        <v>531</v>
       </c>
       <c r="D6" t="n">
-        <v>760</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>5391</v>
       </c>
       <c r="C2" t="n">
-        <v>4075</v>
+        <v>3124</v>
       </c>
       <c r="D2" t="n">
-        <v>29148</v>
+        <v>22738</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3757</v>
+        <v>4408</v>
       </c>
       <c r="C3" t="n">
-        <v>6636</v>
+        <v>4967</v>
       </c>
       <c r="D3" t="n">
-        <v>11755</v>
+        <v>10182</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1910</v>
+        <v>2419</v>
       </c>
       <c r="C4" t="n">
-        <v>5364</v>
+        <v>4174</v>
       </c>
       <c r="D4" t="n">
-        <v>3458</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1043</v>
+        <v>1335</v>
       </c>
       <c r="C5" t="n">
-        <v>3151</v>
+        <v>1893</v>
       </c>
       <c r="D5" t="n">
-        <v>1415</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>524</v>
+        <v>607</v>
       </c>
       <c r="C6" t="n">
-        <v>1872</v>
+        <v>911</v>
       </c>
       <c r="D6" t="n">
-        <v>821</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C7" t="n">
-        <v>714</v>
+        <v>417</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4267</v>
+        <v>5121</v>
       </c>
       <c r="C2" t="n">
-        <v>9276</v>
+        <v>4981</v>
       </c>
       <c r="D2" t="n">
-        <v>32605</v>
+        <v>17880</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3656</v>
+        <v>4039</v>
       </c>
       <c r="C3" t="n">
-        <v>4535</v>
+        <v>3384</v>
       </c>
       <c r="D3" t="n">
-        <v>13691</v>
+        <v>11542</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2414</v>
+        <v>2966</v>
       </c>
       <c r="C4" t="n">
-        <v>5972</v>
+        <v>4551</v>
       </c>
       <c r="D4" t="n">
-        <v>4945</v>
+        <v>5197</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1301</v>
+        <v>1651</v>
       </c>
       <c r="C5" t="n">
-        <v>4266</v>
+        <v>3127</v>
       </c>
       <c r="D5" t="n">
-        <v>1731</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>709</v>
+        <v>894</v>
       </c>
       <c r="C6" t="n">
-        <v>2537</v>
+        <v>1446</v>
       </c>
       <c r="D6" t="n">
-        <v>917</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="C7" t="n">
-        <v>1326</v>
+        <v>687</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>498</v>
+        <v>335</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_32_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5578</v>
+        <v>4772</v>
       </c>
       <c r="C2" t="n">
-        <v>4748</v>
+        <v>10114</v>
       </c>
       <c r="D2" t="n">
-        <v>17592</v>
+        <v>31917</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3755</v>
+        <v>3349</v>
       </c>
       <c r="C3" t="n">
-        <v>3668</v>
+        <v>4027</v>
       </c>
       <c r="D3" t="n">
-        <v>11692</v>
+        <v>16279</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3016</v>
+        <v>2516</v>
       </c>
       <c r="C4" t="n">
-        <v>3817</v>
+        <v>5746</v>
       </c>
       <c r="D4" t="n">
-        <v>6146</v>
+        <v>8125</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2001</v>
+        <v>1593</v>
       </c>
       <c r="C5" t="n">
-        <v>3783</v>
+        <v>4948</v>
       </c>
       <c r="D5" t="n">
-        <v>2591</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1157</v>
+        <v>926</v>
       </c>
       <c r="C6" t="n">
-        <v>2301</v>
+        <v>3135</v>
       </c>
       <c r="D6" t="n">
-        <v>1173</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>545</v>
+        <v>434</v>
       </c>
       <c r="C7" t="n">
-        <v>1073</v>
+        <v>1955</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="C8" t="n">
-        <v>504</v>
+        <v>976</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>416</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8509</v>
+        <v>5012</v>
       </c>
       <c r="C2" t="n">
-        <v>10542</v>
+        <v>10290</v>
       </c>
       <c r="D2" t="n">
-        <v>18005</v>
+        <v>34792</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3755</v>
+        <v>3248</v>
       </c>
       <c r="C3" t="n">
-        <v>3668</v>
+        <v>5936</v>
       </c>
       <c r="D3" t="n">
-        <v>11737</v>
+        <v>17311</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2872</v>
+        <v>2477</v>
       </c>
       <c r="C4" t="n">
-        <v>3625</v>
+        <v>4817</v>
       </c>
       <c r="D4" t="n">
-        <v>6917</v>
+        <v>9208</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2195</v>
+        <v>1748</v>
       </c>
       <c r="C5" t="n">
-        <v>3721</v>
+        <v>5157</v>
       </c>
       <c r="D5" t="n">
-        <v>3067</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1399</v>
+        <v>1098</v>
       </c>
       <c r="C6" t="n">
-        <v>2988</v>
+        <v>3905</v>
       </c>
       <c r="D6" t="n">
-        <v>1388</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>734</v>
+        <v>577</v>
       </c>
       <c r="C7" t="n">
-        <v>1639</v>
+        <v>2443</v>
       </c>
       <c r="D7" t="n">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>313</v>
+        <v>241</v>
       </c>
       <c r="C8" t="n">
-        <v>765</v>
+        <v>1388</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>374</v>
+        <v>636</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10186</v>
+        <v>7428</v>
       </c>
       <c r="C2" t="n">
-        <v>7991</v>
+        <v>12086</v>
       </c>
       <c r="D2" t="n">
-        <v>16184</v>
+        <v>30171</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4678</v>
+        <v>3226</v>
       </c>
       <c r="C3" t="n">
-        <v>5928</v>
+        <v>6813</v>
       </c>
       <c r="D3" t="n">
-        <v>11800</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>2374</v>
       </c>
       <c r="C4" t="n">
-        <v>3535</v>
+        <v>5143</v>
       </c>
       <c r="D4" t="n">
-        <v>7493</v>
+        <v>10006</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2236</v>
+        <v>1809</v>
       </c>
       <c r="C5" t="n">
-        <v>3599</v>
+        <v>4859</v>
       </c>
       <c r="D5" t="n">
-        <v>3535</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1585</v>
+        <v>1245</v>
       </c>
       <c r="C6" t="n">
-        <v>3253</v>
+        <v>4375</v>
       </c>
       <c r="D6" t="n">
-        <v>1627</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>912</v>
+        <v>697</v>
       </c>
       <c r="C7" t="n">
-        <v>2233</v>
+        <v>2991</v>
       </c>
       <c r="D7" t="n">
-        <v>826</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>435</v>
+        <v>324</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1777</v>
       </c>
       <c r="D8" t="n">
-        <v>508</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>534</v>
+        <v>915</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>412</v>
       </c>
       <c r="D10" t="n">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="D11" t="n">
         <v>205</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9038</v>
+        <v>6664</v>
       </c>
       <c r="C2" t="n">
-        <v>5178</v>
+        <v>8315</v>
       </c>
       <c r="D2" t="n">
-        <v>13157</v>
+        <v>25015</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5476</v>
+        <v>4056</v>
       </c>
       <c r="C3" t="n">
-        <v>8229</v>
+        <v>10066</v>
       </c>
       <c r="D3" t="n">
-        <v>13275</v>
+        <v>19763</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2066</v>
+        <v>1671</v>
       </c>
       <c r="C4" t="n">
-        <v>5525</v>
+        <v>7429</v>
       </c>
       <c r="D4" t="n">
-        <v>7410</v>
+        <v>9643</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1464</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="n">
-        <v>3187</v>
+        <v>4287</v>
       </c>
       <c r="D5" t="n">
-        <v>2612</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>842</v>
+        <v>644</v>
       </c>
       <c r="C6" t="n">
-        <v>2188</v>
+        <v>2931</v>
       </c>
       <c r="D6" t="n">
-        <v>809</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>299</v>
       </c>
       <c r="C7" t="n">
-        <v>1102</v>
+        <v>1741</v>
       </c>
       <c r="D7" t="n">
-        <v>497</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>523</v>
+        <v>896</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>403</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
         <v>200</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>81</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5267</v>
+        <v>4038</v>
       </c>
       <c r="C2" t="n">
-        <v>2165</v>
+        <v>3800</v>
       </c>
       <c r="D2" t="n">
-        <v>10219</v>
+        <v>17343</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6048</v>
+        <v>4447</v>
       </c>
       <c r="C3" t="n">
-        <v>6070</v>
+        <v>8514</v>
       </c>
       <c r="D3" t="n">
-        <v>12472</v>
+        <v>19528</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2993</v>
+        <v>2222</v>
       </c>
       <c r="C4" t="n">
-        <v>6972</v>
+        <v>8678</v>
       </c>
       <c r="D4" t="n">
-        <v>8284</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1629</v>
+        <v>1266</v>
       </c>
       <c r="C5" t="n">
-        <v>4306</v>
+        <v>5670</v>
       </c>
       <c r="D5" t="n">
-        <v>3227</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1020</v>
+        <v>766</v>
       </c>
       <c r="C6" t="n">
-        <v>2694</v>
+        <v>3537</v>
       </c>
       <c r="D6" t="n">
-        <v>1013</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>1507</v>
+        <v>2208</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>711</v>
+        <v>1156</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>450</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5824</v>
+        <v>3766</v>
       </c>
       <c r="C2" t="n">
-        <v>5026</v>
+        <v>10377</v>
       </c>
       <c r="D2" t="n">
-        <v>9982</v>
+        <v>24769</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4823</v>
+        <v>3592</v>
       </c>
       <c r="C3" t="n">
-        <v>3574</v>
+        <v>5637</v>
       </c>
       <c r="D3" t="n">
-        <v>11371</v>
+        <v>17918</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3746</v>
+        <v>2727</v>
       </c>
       <c r="C4" t="n">
-        <v>6417</v>
+        <v>8418</v>
       </c>
       <c r="D4" t="n">
-        <v>8755</v>
+        <v>11975</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1989</v>
+        <v>1479</v>
       </c>
       <c r="C5" t="n">
-        <v>5547</v>
+        <v>6938</v>
       </c>
       <c r="D5" t="n">
-        <v>3954</v>
+        <v>4773</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1199</v>
+        <v>890</v>
       </c>
       <c r="C6" t="n">
-        <v>3466</v>
+        <v>4479</v>
       </c>
       <c r="D6" t="n">
-        <v>1339</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>577</v>
+        <v>412</v>
       </c>
       <c r="C7" t="n">
-        <v>2067</v>
+        <v>2767</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>1060</v>
+        <v>1589</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>494</v>
+        <v>721</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>103</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3355</v>
+        <v>2256</v>
       </c>
       <c r="C2" t="n">
-        <v>2199</v>
+        <v>4945</v>
       </c>
       <c r="D2" t="n">
-        <v>6854</v>
+        <v>17261</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4901</v>
+        <v>3506</v>
       </c>
       <c r="C3" t="n">
-        <v>3976</v>
+        <v>7029</v>
       </c>
       <c r="D3" t="n">
-        <v>10913</v>
+        <v>18229</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4202</v>
+        <v>3008</v>
       </c>
       <c r="C4" t="n">
-        <v>5862</v>
+        <v>8170</v>
       </c>
       <c r="D4" t="n">
-        <v>9185</v>
+        <v>12745</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2112</v>
+        <v>1548</v>
       </c>
       <c r="C5" t="n">
-        <v>6515</v>
+        <v>8354</v>
       </c>
       <c r="D5" t="n">
-        <v>4347</v>
+        <v>5036</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1053</v>
+        <v>734</v>
       </c>
       <c r="C6" t="n">
-        <v>4395</v>
+        <v>5287</v>
       </c>
       <c r="D6" t="n">
-        <v>1323</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="C7" t="n">
-        <v>2123</v>
+        <v>2906</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>837</v>
+        <v>1173</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4128</v>
+        <v>2843</v>
       </c>
       <c r="C2" t="n">
-        <v>4396</v>
+        <v>6203</v>
       </c>
       <c r="D2" t="n">
-        <v>10865</v>
+        <v>14105</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3602</v>
+        <v>2573</v>
       </c>
       <c r="C3" t="n">
-        <v>2743</v>
+        <v>5447</v>
       </c>
       <c r="D3" t="n">
-        <v>9577</v>
+        <v>17047</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3937</v>
+        <v>2800</v>
       </c>
       <c r="C4" t="n">
-        <v>4836</v>
+        <v>7474</v>
       </c>
       <c r="D4" t="n">
-        <v>9204</v>
+        <v>13199</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2664</v>
+        <v>1883</v>
       </c>
       <c r="C5" t="n">
-        <v>6128</v>
+        <v>8179</v>
       </c>
       <c r="D5" t="n">
-        <v>5046</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1364</v>
+        <v>945</v>
       </c>
       <c r="C6" t="n">
-        <v>5351</v>
+        <v>6609</v>
       </c>
       <c r="D6" t="n">
-        <v>1740</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>271</v>
       </c>
       <c r="C7" t="n">
-        <v>3143</v>
+        <v>3843</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1357</v>
+        <v>1806</v>
       </c>
       <c r="D8" t="n">
-        <v>418</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>581</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
         <v>47</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3016</v>
+        <v>1928</v>
       </c>
       <c r="C2" t="n">
-        <v>2810</v>
+        <v>3690</v>
       </c>
       <c r="D2" t="n">
-        <v>8222</v>
+        <v>10983</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3311</v>
+        <v>2329</v>
       </c>
       <c r="C3" t="n">
-        <v>3110</v>
+        <v>5219</v>
       </c>
       <c r="D3" t="n">
-        <v>9205</v>
+        <v>15930</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3494</v>
+        <v>2520</v>
       </c>
       <c r="C4" t="n">
-        <v>3950</v>
+        <v>6735</v>
       </c>
       <c r="D4" t="n">
-        <v>9066</v>
+        <v>13404</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2939</v>
+        <v>2032</v>
       </c>
       <c r="C5" t="n">
-        <v>5727</v>
+        <v>8000</v>
       </c>
       <c r="D5" t="n">
-        <v>5508</v>
+        <v>6686</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1635</v>
+        <v>1104</v>
       </c>
       <c r="C6" t="n">
-        <v>5834</v>
+        <v>7356</v>
       </c>
       <c r="D6" t="n">
-        <v>2070</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>243</v>
       </c>
       <c r="C7" t="n">
-        <v>3963</v>
+        <v>4755</v>
       </c>
       <c r="D7" t="n">
-        <v>803</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1813</v>
+        <v>2298</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>606</v>
+        <v>656</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5406</v>
+        <v>3008</v>
       </c>
       <c r="C2" t="n">
-        <v>4847</v>
+        <v>12284</v>
       </c>
       <c r="D2" t="n">
-        <v>17737</v>
+        <v>12426</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2685</v>
+        <v>1845</v>
       </c>
       <c r="C3" t="n">
-        <v>2631</v>
+        <v>4125</v>
       </c>
       <c r="D3" t="n">
-        <v>8475</v>
+        <v>14469</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2975</v>
+        <v>2154</v>
       </c>
       <c r="C4" t="n">
-        <v>3480</v>
+        <v>5969</v>
       </c>
       <c r="D4" t="n">
-        <v>8811</v>
+        <v>13207</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2893</v>
+        <v>2001</v>
       </c>
       <c r="C5" t="n">
-        <v>4823</v>
+        <v>7335</v>
       </c>
       <c r="D5" t="n">
-        <v>5800</v>
+        <v>7385</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1965</v>
+        <v>1307</v>
       </c>
       <c r="C6" t="n">
-        <v>5735</v>
+        <v>7536</v>
       </c>
       <c r="D6" t="n">
-        <v>2537</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>751</v>
+        <v>446</v>
       </c>
       <c r="C7" t="n">
-        <v>4770</v>
+        <v>5696</v>
       </c>
       <c r="D7" t="n">
-        <v>968</v>
+        <v>920</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>2651</v>
+        <v>3162</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1031</v>
+        <v>1177</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5391</v>
+        <v>5099</v>
       </c>
       <c r="C2" t="n">
-        <v>2983</v>
+        <v>10164</v>
       </c>
       <c r="D2" t="n">
-        <v>15770</v>
+        <v>14007</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3743</v>
+        <v>2173</v>
       </c>
       <c r="C2" t="n">
-        <v>2636</v>
+        <v>7174</v>
       </c>
       <c r="D2" t="n">
-        <v>12912</v>
+        <v>9245</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3780</v>
+        <v>2528</v>
       </c>
       <c r="C3" t="n">
-        <v>3412</v>
+        <v>6256</v>
       </c>
       <c r="D3" t="n">
-        <v>9920</v>
+        <v>15473</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4160</v>
+        <v>2931</v>
       </c>
       <c r="C4" t="n">
-        <v>5037</v>
+        <v>8480</v>
       </c>
       <c r="D4" t="n">
-        <v>9231</v>
+        <v>13563</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1976</v>
+        <v>1244</v>
       </c>
       <c r="C5" t="n">
-        <v>7614</v>
+        <v>10629</v>
       </c>
       <c r="D5" t="n">
-        <v>5505</v>
+        <v>6688</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>693</v>
+        <v>412</v>
       </c>
       <c r="C6" t="n">
-        <v>5967</v>
+        <v>6985</v>
       </c>
       <c r="D6" t="n">
-        <v>2083</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>2597</v>
+        <v>3098</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1010</v>
+        <v>1153</v>
       </c>
       <c r="D8" t="n">
-        <v>309</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7680</v>
+        <v>6601</v>
       </c>
       <c r="C2" t="n">
-        <v>3173</v>
+        <v>4869</v>
       </c>
       <c r="D2" t="n">
-        <v>16112</v>
+        <v>22347</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2291</v>
+        <v>2167</v>
       </c>
       <c r="C3" t="n">
-        <v>1503</v>
+        <v>5122</v>
       </c>
       <c r="D3" t="n">
-        <v>3288</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5179</v>
+        <v>4326</v>
       </c>
       <c r="C2" t="n">
-        <v>3634</v>
+        <v>5284</v>
       </c>
       <c r="D2" t="n">
-        <v>14315</v>
+        <v>27597</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4089</v>
+        <v>3597</v>
       </c>
       <c r="C3" t="n">
-        <v>2122</v>
+        <v>4293</v>
       </c>
       <c r="D3" t="n">
-        <v>5200</v>
+        <v>6023</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1029</v>
+        <v>975</v>
       </c>
       <c r="C4" t="n">
-        <v>939</v>
+        <v>3045</v>
       </c>
       <c r="D4" t="n">
-        <v>1844</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5582</v>
+        <v>4497</v>
       </c>
       <c r="C2" t="n">
-        <v>5612</v>
+        <v>8202</v>
       </c>
       <c r="D2" t="n">
-        <v>13934</v>
+        <v>20136</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3848</v>
+        <v>3258</v>
       </c>
       <c r="C3" t="n">
-        <v>2550</v>
+        <v>4182</v>
       </c>
       <c r="D3" t="n">
-        <v>6284</v>
+        <v>9041</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2162</v>
+        <v>1941</v>
       </c>
       <c r="C4" t="n">
-        <v>1580</v>
+        <v>3647</v>
       </c>
       <c r="D4" t="n">
-        <v>2414</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="C5" t="n">
-        <v>616</v>
+        <v>1763</v>
       </c>
       <c r="D5" t="n">
-        <v>1276</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5859</v>
+        <v>5018</v>
       </c>
       <c r="C2" t="n">
-        <v>9174</v>
+        <v>7728</v>
       </c>
       <c r="D2" t="n">
-        <v>20362</v>
+        <v>32085</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3848</v>
+        <v>3153</v>
       </c>
       <c r="C3" t="n">
-        <v>3611</v>
+        <v>5440</v>
       </c>
       <c r="D3" t="n">
-        <v>7004</v>
+        <v>10090</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2568</v>
+        <v>2186</v>
       </c>
       <c r="C4" t="n">
-        <v>2077</v>
+        <v>3858</v>
       </c>
       <c r="D4" t="n">
-        <v>3023</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1092</v>
+        <v>982</v>
       </c>
       <c r="C5" t="n">
-        <v>1106</v>
+        <v>2702</v>
       </c>
       <c r="D5" t="n">
-        <v>1444</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>461</v>
+        <v>1026</v>
       </c>
       <c r="D6" t="n">
         <v>955</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
         <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7006</v>
+        <v>5637</v>
       </c>
       <c r="C2" t="n">
-        <v>6110</v>
+        <v>11145</v>
       </c>
       <c r="D2" t="n">
-        <v>23671</v>
+        <v>30782</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3527</v>
+        <v>2949</v>
       </c>
       <c r="C3" t="n">
-        <v>5328</v>
+        <v>5399</v>
       </c>
       <c r="D3" t="n">
-        <v>8035</v>
+        <v>11969</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1990</v>
+        <v>1658</v>
       </c>
       <c r="C4" t="n">
-        <v>2393</v>
+        <v>3828</v>
       </c>
       <c r="D4" t="n">
-        <v>3163</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>965</v>
+        <v>819</v>
       </c>
       <c r="C5" t="n">
-        <v>1192</v>
+        <v>2408</v>
       </c>
       <c r="D5" t="n">
-        <v>1368</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>531</v>
+        <v>1242</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>262</v>
+        <v>436</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5983,10 +5983,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6028,7 +6028,7 @@
         <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5391</v>
+        <v>5423</v>
       </c>
       <c r="C2" t="n">
-        <v>3124</v>
+        <v>5676</v>
       </c>
       <c r="D2" t="n">
-        <v>22738</v>
+        <v>25220</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4408</v>
+        <v>3551</v>
       </c>
       <c r="C3" t="n">
-        <v>4967</v>
+        <v>7586</v>
       </c>
       <c r="D3" t="n">
-        <v>10182</v>
+        <v>14248</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2419</v>
+        <v>2012</v>
       </c>
       <c r="C4" t="n">
-        <v>4174</v>
+        <v>4646</v>
       </c>
       <c r="D4" t="n">
-        <v>4095</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1335</v>
+        <v>1092</v>
       </c>
       <c r="C5" t="n">
-        <v>1893</v>
+        <v>3189</v>
       </c>
       <c r="D5" t="n">
-        <v>1675</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>607</v>
+        <v>513</v>
       </c>
       <c r="C6" t="n">
-        <v>911</v>
+        <v>1887</v>
       </c>
       <c r="D6" t="n">
-        <v>889</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>417</v>
+        <v>886</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5121</v>
+        <v>4562</v>
       </c>
       <c r="C2" t="n">
-        <v>4981</v>
+        <v>3442</v>
       </c>
       <c r="D2" t="n">
-        <v>17880</v>
+        <v>31179</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4039</v>
+        <v>3655</v>
       </c>
       <c r="C3" t="n">
-        <v>3384</v>
+        <v>5692</v>
       </c>
       <c r="D3" t="n">
-        <v>11542</v>
+        <v>14977</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2966</v>
+        <v>2360</v>
       </c>
       <c r="C4" t="n">
-        <v>4551</v>
+        <v>6186</v>
       </c>
       <c r="D4" t="n">
-        <v>5197</v>
+        <v>7035</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1651</v>
+        <v>1360</v>
       </c>
       <c r="C5" t="n">
-        <v>3127</v>
+        <v>3875</v>
       </c>
       <c r="D5" t="n">
-        <v>2088</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>894</v>
+        <v>719</v>
       </c>
       <c r="C6" t="n">
-        <v>1446</v>
+        <v>2552</v>
       </c>
       <c r="D6" t="n">
-        <v>1011</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>299</v>
       </c>
       <c r="C7" t="n">
-        <v>687</v>
+        <v>1405</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>335</v>
+        <v>611</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_32_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>800</v>
       </c>
       <c r="C2" t="n">
-        <v>10114</v>
+        <v>2387</v>
       </c>
       <c r="D2" t="n">
-        <v>31917</v>
+        <v>16206</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3349</v>
+        <v>1239</v>
       </c>
       <c r="C3" t="n">
-        <v>4027</v>
+        <v>6332</v>
       </c>
       <c r="D3" t="n">
-        <v>16279</v>
+        <v>17277</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2516</v>
+        <v>807</v>
       </c>
       <c r="C4" t="n">
-        <v>5746</v>
+        <v>7988</v>
       </c>
       <c r="D4" t="n">
-        <v>8125</v>
+        <v>7573</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1593</v>
+        <v>414</v>
       </c>
       <c r="C5" t="n">
-        <v>4948</v>
+        <v>5287</v>
       </c>
       <c r="D5" t="n">
-        <v>3223</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>926</v>
+        <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>3135</v>
+        <v>2092</v>
       </c>
       <c r="D6" t="n">
-        <v>1278</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>434</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1955</v>
+        <v>755</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>976</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>416</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5012</v>
+        <v>776</v>
       </c>
       <c r="C2" t="n">
-        <v>10290</v>
+        <v>6277</v>
       </c>
       <c r="D2" t="n">
-        <v>34792</v>
+        <v>15609</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3248</v>
+        <v>870</v>
       </c>
       <c r="C3" t="n">
-        <v>5936</v>
+        <v>3763</v>
       </c>
       <c r="D3" t="n">
-        <v>17311</v>
+        <v>15897</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2477</v>
+        <v>877</v>
       </c>
       <c r="C4" t="n">
-        <v>4817</v>
+        <v>6931</v>
       </c>
       <c r="D4" t="n">
-        <v>9208</v>
+        <v>9112</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1748</v>
+        <v>525</v>
       </c>
       <c r="C5" t="n">
-        <v>5157</v>
+        <v>6627</v>
       </c>
       <c r="D5" t="n">
-        <v>3847</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1098</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>3905</v>
+        <v>3654</v>
       </c>
       <c r="D6" t="n">
-        <v>1559</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>577</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>2443</v>
+        <v>1391</v>
       </c>
       <c r="D7" t="n">
-        <v>742</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1388</v>
+        <v>534</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>636</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7428</v>
+        <v>409</v>
       </c>
       <c r="C2" t="n">
-        <v>12086</v>
+        <v>2677</v>
       </c>
       <c r="D2" t="n">
-        <v>30171</v>
+        <v>10654</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3226</v>
+        <v>818</v>
       </c>
       <c r="C3" t="n">
-        <v>6813</v>
+        <v>4577</v>
       </c>
       <c r="D3" t="n">
-        <v>18300</v>
+        <v>15455</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2374</v>
+        <v>958</v>
       </c>
       <c r="C4" t="n">
-        <v>5143</v>
+        <v>6302</v>
       </c>
       <c r="D4" t="n">
-        <v>10006</v>
+        <v>9988</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1809</v>
+        <v>534</v>
       </c>
       <c r="C5" t="n">
-        <v>4859</v>
+        <v>7494</v>
       </c>
       <c r="D5" t="n">
-        <v>4502</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1245</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
-        <v>4375</v>
+        <v>4626</v>
       </c>
       <c r="D6" t="n">
-        <v>1830</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>697</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>2991</v>
+        <v>1316</v>
       </c>
       <c r="D7" t="n">
-        <v>846</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>324</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1777</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>915</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>412</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6664</v>
+        <v>306</v>
       </c>
       <c r="C2" t="n">
-        <v>8315</v>
+        <v>5746</v>
       </c>
       <c r="D2" t="n">
-        <v>25015</v>
+        <v>9639</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4056</v>
+        <v>544</v>
       </c>
       <c r="C3" t="n">
-        <v>10066</v>
+        <v>3199</v>
       </c>
       <c r="D3" t="n">
-        <v>19763</v>
+        <v>13785</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1671</v>
+        <v>789</v>
       </c>
       <c r="C4" t="n">
-        <v>7429</v>
+        <v>5337</v>
       </c>
       <c r="D4" t="n">
-        <v>9643</v>
+        <v>10629</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1150</v>
+        <v>647</v>
       </c>
       <c r="C5" t="n">
-        <v>4287</v>
+        <v>6826</v>
       </c>
       <c r="D5" t="n">
-        <v>3003</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>644</v>
+        <v>320</v>
       </c>
       <c r="C6" t="n">
-        <v>2931</v>
+        <v>5946</v>
       </c>
       <c r="D6" t="n">
-        <v>829</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>1741</v>
+        <v>2800</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>896</v>
+        <v>841</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>403</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4038</v>
+        <v>204</v>
       </c>
       <c r="C2" t="n">
         <v>3800</v>
       </c>
       <c r="D2" t="n">
-        <v>17343</v>
+        <v>8568</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4447</v>
+        <v>399</v>
       </c>
       <c r="C3" t="n">
-        <v>8514</v>
+        <v>3895</v>
       </c>
       <c r="D3" t="n">
-        <v>19528</v>
+        <v>12559</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2222</v>
+        <v>652</v>
       </c>
       <c r="C4" t="n">
-        <v>8678</v>
+        <v>4394</v>
       </c>
       <c r="D4" t="n">
-        <v>10899</v>
+        <v>10862</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1266</v>
+        <v>677</v>
       </c>
       <c r="C5" t="n">
-        <v>5670</v>
+        <v>6331</v>
       </c>
       <c r="D5" t="n">
-        <v>3798</v>
+        <v>5116</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>389</v>
       </c>
       <c r="C6" t="n">
-        <v>3537</v>
+        <v>6561</v>
       </c>
       <c r="D6" t="n">
-        <v>1060</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>2208</v>
+        <v>3885</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1156</v>
+        <v>1302</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3766</v>
+        <v>274</v>
       </c>
       <c r="C2" t="n">
-        <v>10377</v>
+        <v>16479</v>
       </c>
       <c r="D2" t="n">
-        <v>24769</v>
+        <v>13211</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3592</v>
+        <v>270</v>
       </c>
       <c r="C3" t="n">
-        <v>5637</v>
+        <v>3389</v>
       </c>
       <c r="D3" t="n">
-        <v>17918</v>
+        <v>11172</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2727</v>
+        <v>480</v>
       </c>
       <c r="C4" t="n">
-        <v>8418</v>
+        <v>4105</v>
       </c>
       <c r="D4" t="n">
-        <v>11975</v>
+        <v>10808</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1479</v>
+        <v>617</v>
       </c>
       <c r="C5" t="n">
-        <v>6938</v>
+        <v>5325</v>
       </c>
       <c r="D5" t="n">
-        <v>4773</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>890</v>
+        <v>463</v>
       </c>
       <c r="C6" t="n">
-        <v>4479</v>
+        <v>6399</v>
       </c>
       <c r="D6" t="n">
-        <v>1440</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>2767</v>
+        <v>5049</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>805</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1589</v>
+        <v>2326</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>721</v>
+        <v>753</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2256</v>
+        <v>186</v>
       </c>
       <c r="C2" t="n">
-        <v>4945</v>
+        <v>8701</v>
       </c>
       <c r="D2" t="n">
-        <v>17261</v>
+        <v>9618</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3506</v>
+        <v>397</v>
       </c>
       <c r="C3" t="n">
-        <v>7029</v>
+        <v>7215</v>
       </c>
       <c r="D3" t="n">
-        <v>18229</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3008</v>
+        <v>804</v>
       </c>
       <c r="C4" t="n">
-        <v>8170</v>
+        <v>5892</v>
       </c>
       <c r="D4" t="n">
-        <v>12745</v>
+        <v>11147</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1548</v>
+        <v>467</v>
       </c>
       <c r="C5" t="n">
-        <v>8354</v>
+        <v>8446</v>
       </c>
       <c r="D5" t="n">
-        <v>5036</v>
+        <v>5342</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>734</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
-        <v>5287</v>
+        <v>6453</v>
       </c>
       <c r="D6" t="n">
-        <v>1400</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>2906</v>
+        <v>2279</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1173</v>
+        <v>737</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2843</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>6203</v>
+        <v>4884</v>
       </c>
       <c r="D2" t="n">
-        <v>14105</v>
+        <v>6714</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2573</v>
+        <v>262</v>
       </c>
       <c r="C3" t="n">
-        <v>5447</v>
+        <v>6993</v>
       </c>
       <c r="D3" t="n">
-        <v>17047</v>
+        <v>10949</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2800</v>
+        <v>522</v>
       </c>
       <c r="C4" t="n">
-        <v>7474</v>
+        <v>6219</v>
       </c>
       <c r="D4" t="n">
-        <v>13199</v>
+        <v>10543</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1883</v>
+        <v>433</v>
       </c>
       <c r="C5" t="n">
-        <v>8179</v>
+        <v>6381</v>
       </c>
       <c r="D5" t="n">
-        <v>5993</v>
+        <v>5563</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>945</v>
+        <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>6609</v>
+        <v>6060</v>
       </c>
       <c r="D6" t="n">
-        <v>1884</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>3843</v>
+        <v>2901</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1806</v>
+        <v>851</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>581</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1928</v>
+        <v>174</v>
       </c>
       <c r="C2" t="n">
-        <v>3690</v>
+        <v>4229</v>
       </c>
       <c r="D2" t="n">
-        <v>10983</v>
+        <v>13175</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2329</v>
+        <v>154</v>
       </c>
       <c r="C3" t="n">
-        <v>5219</v>
+        <v>5113</v>
       </c>
       <c r="D3" t="n">
-        <v>15930</v>
+        <v>9534</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2520</v>
+        <v>353</v>
       </c>
       <c r="C4" t="n">
-        <v>6735</v>
+        <v>6513</v>
       </c>
       <c r="D4" t="n">
-        <v>13404</v>
+        <v>10296</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2032</v>
+        <v>431</v>
       </c>
       <c r="C5" t="n">
-        <v>8000</v>
+        <v>6223</v>
       </c>
       <c r="D5" t="n">
-        <v>6686</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1104</v>
+        <v>261</v>
       </c>
       <c r="C6" t="n">
-        <v>7356</v>
+        <v>6154</v>
       </c>
       <c r="D6" t="n">
-        <v>2214</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>243</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>4755</v>
+        <v>4476</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>789</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>2298</v>
+        <v>1803</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>656</v>
+        <v>525</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3008</v>
+        <v>281</v>
       </c>
       <c r="C2" t="n">
-        <v>12284</v>
+        <v>17003</v>
       </c>
       <c r="D2" t="n">
-        <v>12426</v>
+        <v>24489</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1845</v>
+        <v>134</v>
       </c>
       <c r="C3" t="n">
-        <v>4125</v>
+        <v>4115</v>
       </c>
       <c r="D3" t="n">
-        <v>14469</v>
+        <v>9402</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2154</v>
+        <v>233</v>
       </c>
       <c r="C4" t="n">
-        <v>5969</v>
+        <v>5678</v>
       </c>
       <c r="D4" t="n">
-        <v>13207</v>
+        <v>9851</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2001</v>
+        <v>362</v>
       </c>
       <c r="C5" t="n">
-        <v>7335</v>
+        <v>6232</v>
       </c>
       <c r="D5" t="n">
-        <v>7385</v>
+        <v>6723</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1307</v>
+        <v>308</v>
       </c>
       <c r="C6" t="n">
-        <v>7536</v>
+        <v>6063</v>
       </c>
       <c r="D6" t="n">
-        <v>2743</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>446</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>5696</v>
+        <v>5247</v>
       </c>
       <c r="D7" t="n">
-        <v>920</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>3162</v>
+        <v>2981</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1177</v>
+        <v>1063</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5099</v>
+        <v>2058</v>
       </c>
       <c r="C2" t="n">
-        <v>10164</v>
+        <v>11482</v>
       </c>
       <c r="D2" t="n">
-        <v>14007</v>
+        <v>11856</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2173</v>
+        <v>469</v>
       </c>
       <c r="C2" t="n">
-        <v>7174</v>
+        <v>13324</v>
       </c>
       <c r="D2" t="n">
-        <v>9245</v>
+        <v>29951</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2528</v>
+        <v>157</v>
       </c>
       <c r="C3" t="n">
-        <v>6256</v>
+        <v>8486</v>
       </c>
       <c r="D3" t="n">
-        <v>15473</v>
+        <v>10716</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2931</v>
+        <v>169</v>
       </c>
       <c r="C4" t="n">
-        <v>8480</v>
+        <v>4854</v>
       </c>
       <c r="D4" t="n">
-        <v>13563</v>
+        <v>9482</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1244</v>
+        <v>287</v>
       </c>
       <c r="C5" t="n">
-        <v>10629</v>
+        <v>5863</v>
       </c>
       <c r="D5" t="n">
-        <v>6688</v>
+        <v>6904</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>412</v>
+        <v>308</v>
       </c>
       <c r="C6" t="n">
-        <v>6985</v>
+        <v>6018</v>
       </c>
       <c r="D6" t="n">
-        <v>2101</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="C7" t="n">
-        <v>3098</v>
+        <v>5580</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1153</v>
+        <v>3838</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>1795</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>587</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6601</v>
+        <v>3260</v>
       </c>
       <c r="C2" t="n">
-        <v>4869</v>
+        <v>9112</v>
       </c>
       <c r="D2" t="n">
-        <v>22347</v>
+        <v>26716</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2167</v>
+        <v>683</v>
       </c>
       <c r="C3" t="n">
-        <v>5122</v>
+        <v>4534</v>
       </c>
       <c r="D3" t="n">
-        <v>2992</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4326</v>
+        <v>1804</v>
       </c>
       <c r="C2" t="n">
-        <v>5284</v>
+        <v>6883</v>
       </c>
       <c r="D2" t="n">
-        <v>27597</v>
+        <v>25868</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3597</v>
+        <v>1676</v>
       </c>
       <c r="C3" t="n">
-        <v>4293</v>
+        <v>6261</v>
       </c>
       <c r="D3" t="n">
-        <v>6023</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>975</v>
+        <v>343</v>
       </c>
       <c r="C4" t="n">
-        <v>3045</v>
+        <v>2876</v>
       </c>
       <c r="D4" t="n">
-        <v>1784</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4497</v>
+        <v>1367</v>
       </c>
       <c r="C2" t="n">
-        <v>8202</v>
+        <v>8487</v>
       </c>
       <c r="D2" t="n">
-        <v>20136</v>
+        <v>25328</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3258</v>
+        <v>1435</v>
       </c>
       <c r="C3" t="n">
-        <v>4182</v>
+        <v>5697</v>
       </c>
       <c r="D3" t="n">
-        <v>9041</v>
+        <v>9179</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1941</v>
+        <v>888</v>
       </c>
       <c r="C4" t="n">
-        <v>3647</v>
+        <v>4830</v>
       </c>
       <c r="D4" t="n">
-        <v>2543</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>452</v>
+        <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>1763</v>
+        <v>1740</v>
       </c>
       <c r="D5" t="n">
-        <v>1256</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5018</v>
+        <v>1164</v>
       </c>
       <c r="C2" t="n">
-        <v>7728</v>
+        <v>5152</v>
       </c>
       <c r="D2" t="n">
-        <v>32085</v>
+        <v>34219</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3153</v>
+        <v>1159</v>
       </c>
       <c r="C3" t="n">
-        <v>5440</v>
+        <v>6248</v>
       </c>
       <c r="D3" t="n">
-        <v>10090</v>
+        <v>11101</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2186</v>
+        <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>3858</v>
+        <v>5220</v>
       </c>
       <c r="D4" t="n">
-        <v>3650</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>982</v>
+        <v>452</v>
       </c>
       <c r="C5" t="n">
-        <v>2702</v>
+        <v>3394</v>
       </c>
       <c r="D5" t="n">
-        <v>1428</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="C6" t="n">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5637</v>
+        <v>1322</v>
       </c>
       <c r="C2" t="n">
-        <v>11145</v>
+        <v>5462</v>
       </c>
       <c r="D2" t="n">
-        <v>30782</v>
+        <v>35643</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2949</v>
+        <v>961</v>
       </c>
       <c r="C3" t="n">
-        <v>5399</v>
+        <v>5007</v>
       </c>
       <c r="D3" t="n">
-        <v>11969</v>
+        <v>13833</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1658</v>
+        <v>922</v>
       </c>
       <c r="C4" t="n">
-        <v>3828</v>
+        <v>5604</v>
       </c>
       <c r="D4" t="n">
-        <v>4111</v>
+        <v>4935</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>819</v>
+        <v>621</v>
       </c>
       <c r="C5" t="n">
-        <v>2408</v>
+        <v>4270</v>
       </c>
       <c r="D5" t="n">
-        <v>1421</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>291</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>1242</v>
+        <v>2203</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>436</v>
+        <v>659</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5423</v>
+        <v>1739</v>
       </c>
       <c r="C2" t="n">
-        <v>5676</v>
+        <v>9863</v>
       </c>
       <c r="D2" t="n">
-        <v>25220</v>
+        <v>28952</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3551</v>
+        <v>921</v>
       </c>
       <c r="C3" t="n">
-        <v>7586</v>
+        <v>4579</v>
       </c>
       <c r="D3" t="n">
-        <v>14248</v>
+        <v>16021</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2012</v>
+        <v>807</v>
       </c>
       <c r="C4" t="n">
-        <v>4646</v>
+        <v>5189</v>
       </c>
       <c r="D4" t="n">
-        <v>5530</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1092</v>
+        <v>674</v>
       </c>
       <c r="C5" t="n">
-        <v>3189</v>
+        <v>4780</v>
       </c>
       <c r="D5" t="n">
-        <v>1920</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>513</v>
+        <v>372</v>
       </c>
       <c r="C6" t="n">
-        <v>1887</v>
+        <v>3152</v>
       </c>
       <c r="D6" t="n">
-        <v>898</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>886</v>
+        <v>1369</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>337</v>
+        <v>454</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4562</v>
+        <v>1548</v>
       </c>
       <c r="C2" t="n">
-        <v>3442</v>
+        <v>6154</v>
       </c>
       <c r="D2" t="n">
-        <v>31179</v>
+        <v>23005</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3655</v>
+        <v>1315</v>
       </c>
       <c r="C3" t="n">
-        <v>5692</v>
+        <v>7925</v>
       </c>
       <c r="D3" t="n">
-        <v>14977</v>
+        <v>17295</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2360</v>
+        <v>622</v>
       </c>
       <c r="C4" t="n">
-        <v>6186</v>
+        <v>7776</v>
       </c>
       <c r="D4" t="n">
-        <v>7035</v>
+        <v>5755</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1360</v>
+        <v>343</v>
       </c>
       <c r="C5" t="n">
-        <v>3875</v>
+        <v>3088</v>
       </c>
       <c r="D5" t="n">
-        <v>2520</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>719</v>
+        <v>145</v>
       </c>
       <c r="C6" t="n">
-        <v>2552</v>
+        <v>1341</v>
       </c>
       <c r="D6" t="n">
-        <v>1053</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>1405</v>
+        <v>444</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>611</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
